--- a/InputData/trans/BNoEVC/BAU Number of EV Chargers.xlsx
+++ b/InputData/trans/BNoEVC/BAU Number of EV Chargers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\DE\trans\BNoEVC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/DE/trans/BNoEVC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09F5A5B1-5964-4A3C-9C74-76C9F4DA00EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FE36C94-B9B1-D24F-BC35-0BAB5D5F95B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="5" activeTab="7" xr2:uid="{53BC2858-0C9C-40F6-9AF5-90A6B4092AC8}"/>
+    <workbookView xWindow="400" yWindow="760" windowWidth="13040" windowHeight="16900" firstSheet="5" activeTab="7" xr2:uid="{53BC2858-0C9C-40F6-9AF5-90A6B4092AC8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1274,10 +1274,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1288,7 +1288,7 @@
         <v>56</v>
       </c>
       <c r="C1" s="52">
-        <v>45258</v>
+        <v>45296</v>
       </c>
       <c r="F1" s="51" t="s">
         <v>49</v>
@@ -1770,7 +1770,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F724BD-41BD-447C-BA7D-97E73890547D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1782,9 +1782,9 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1806,7 +1806,7 @@
         <v>7500000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30">
+    <row r="5" spans="1:2" ht="16">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>9375000000</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="16">
       <c r="A6" s="7" t="s">
         <v>37</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>7943476215.0791588</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30">
+    <row r="8" spans="1:2" ht="32">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>24443</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30">
+    <row r="10" spans="1:2" ht="32">
       <c r="A10" s="7" t="s">
         <v>43</v>
       </c>
@@ -1852,16 +1852,16 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL24"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="60.7109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="10" customWidth="1"/>
-    <col min="5" max="6" width="16.140625" style="10" customWidth="1"/>
-    <col min="7" max="11" width="12.5703125" style="10"/>
-    <col min="12" max="12" width="16.42578125" style="10" customWidth="1"/>
-    <col min="13" max="16384" width="12.5703125" style="10"/>
+    <col min="1" max="1" width="60.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="27.5" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="10" customWidth="1"/>
+    <col min="5" max="6" width="16.1640625" style="10" customWidth="1"/>
+    <col min="7" max="11" width="12.5" style="10"/>
+    <col min="12" max="12" width="16.5" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="12.5" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="14.25" customHeight="1">
@@ -1906,7 +1906,7 @@
       <c r="AK1" s="9"/>
       <c r="AL1" s="9"/>
     </row>
-    <row r="2" spans="1:38" ht="180">
+    <row r="2" spans="1:38" ht="160">
       <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
@@ -2136,7 +2136,7 @@
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
     </row>
-    <row r="10" spans="1:38" ht="15">
+    <row r="10" spans="1:38" ht="16">
       <c r="A10" s="17" t="s">
         <v>19</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="AK11" s="16"/>
       <c r="AL11" s="16"/>
     </row>
-    <row r="12" spans="1:38" ht="30">
+    <row r="12" spans="1:38" ht="16">
       <c r="A12" s="17" t="s">
         <v>20</v>
       </c>
@@ -2835,10 +2835,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341A17B3-AFD9-42DA-AB68-E46FC6CF1D40}">
   <dimension ref="A1:AF11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="45.140625" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
+    <col min="1" max="1" width="45.1640625" customWidth="1"/>
+    <col min="2" max="2" width="26.5" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3439,14 +3439,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FE97F2-8705-4D3C-B355-0F6C727EDC4E}">
   <dimension ref="A1:D114"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="21" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" style="21" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="21"/>
+    <col min="1" max="1" width="19.83203125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="32.5" style="21" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.5" thickBot="1">
+    <row r="1" spans="1:4" ht="14" thickBot="1">
       <c r="A1" s="36" t="s">
         <v>45</v>
       </c>
@@ -3466,13 +3466,13 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="13.5" thickBot="1">
+    <row r="4" spans="1:4" ht="14" thickBot="1">
       <c r="A4" s="40"/>
       <c r="B4" s="42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="14">
       <c r="A5" s="26" t="s">
         <v>49</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="13.5" thickBot="1">
+    <row r="6" spans="1:4" ht="14" thickBot="1">
       <c r="A6" s="27"/>
       <c r="B6" s="33">
         <v>35</v>
@@ -3495,7 +3495,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" ht="14">
       <c r="A7" s="30" t="s">
         <v>50</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="13.5" thickBot="1">
+    <row r="8" spans="1:4" ht="14" thickBot="1">
       <c r="A8" s="31"/>
       <c r="B8" s="35">
         <v>3</v>
@@ -3518,7 +3518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="14">
       <c r="A9" s="26" t="s">
         <v>51</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>2638</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="13.5" thickBot="1">
+    <row r="10" spans="1:4" ht="14" thickBot="1">
       <c r="A10" s="27"/>
       <c r="B10" s="33">
         <v>9</v>
@@ -3541,7 +3541,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" ht="14">
       <c r="A11" s="30" t="s">
         <v>52</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="13.5" thickBot="1">
+    <row r="12" spans="1:4" ht="14" thickBot="1">
       <c r="A12" s="31"/>
       <c r="B12" s="35">
         <v>3</v>
@@ -3564,7 +3564,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="14">
       <c r="A13" s="26" t="s">
         <v>53</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>43400</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="13.5" thickBot="1">
+    <row r="14" spans="1:4" ht="14" thickBot="1">
       <c r="A14" s="27"/>
       <c r="B14" s="33">
         <v>546</v>
@@ -3587,7 +3587,7 @@
         <v>8465</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="14">
       <c r="A15" s="30" t="s">
         <v>54</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="13.5" thickBot="1">
+    <row r="16" spans="1:4" ht="14" thickBot="1">
       <c r="A16" s="31"/>
       <c r="B16" s="35">
         <v>90</v>
@@ -3610,7 +3610,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="14">
       <c r="A17" s="26" t="s">
         <v>55</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="13.5" thickBot="1">
+    <row r="18" spans="1:4" ht="14" thickBot="1">
       <c r="A18" s="27"/>
       <c r="B18" s="33">
         <v>67</v>
@@ -3633,7 +3633,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" ht="14">
       <c r="A19" s="30" t="s">
         <v>56</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="13.5" thickBot="1">
+    <row r="20" spans="1:4" ht="14" thickBot="1">
       <c r="A20" s="31"/>
       <c r="B20" s="35">
         <v>5</v>
@@ -3656,7 +3656,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" ht="14">
       <c r="A21" s="26" t="s">
         <v>57</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="13.5" thickBot="1">
+    <row r="22" spans="1:4" ht="14" thickBot="1">
       <c r="A22" s="27"/>
       <c r="B22" s="33">
         <v>43</v>
@@ -3679,7 +3679,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" ht="14">
       <c r="A23" s="30" t="s">
         <v>58</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>7802</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="13.5" thickBot="1">
+    <row r="24" spans="1:4" ht="14" thickBot="1">
       <c r="A24" s="31"/>
       <c r="B24" s="35">
         <v>364</v>
@@ -3702,7 +3702,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" ht="14">
       <c r="A25" s="26" t="s">
         <v>59</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="13.5" thickBot="1">
+    <row r="26" spans="1:4" ht="14" thickBot="1">
       <c r="A26" s="27"/>
       <c r="B26" s="33">
         <v>230</v>
@@ -3725,7 +3725,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="14">
       <c r="A27" s="30" t="s">
         <v>60</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="13.5" thickBot="1">
+    <row r="28" spans="1:4" ht="14" thickBot="1">
       <c r="A28" s="31"/>
       <c r="B28" s="35">
         <v>30</v>
@@ -3748,7 +3748,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" ht="14">
       <c r="A29" s="26" t="s">
         <v>61</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="13.5" thickBot="1">
+    <row r="30" spans="1:4" ht="14" thickBot="1">
       <c r="A30" s="27"/>
       <c r="B30" s="33">
         <v>10</v>
@@ -3771,7 +3771,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" ht="14">
       <c r="A31" s="30" t="s">
         <v>62</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>3315</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="13.5" thickBot="1">
+    <row r="32" spans="1:4" ht="14" thickBot="1">
       <c r="A32" s="31"/>
       <c r="B32" s="35">
         <v>50</v>
@@ -3794,7 +3794,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" ht="14">
       <c r="A33" s="26" t="s">
         <v>63</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="13.5" thickBot="1">
+    <row r="34" spans="1:4" ht="14" thickBot="1">
       <c r="A34" s="27"/>
       <c r="B34" s="33">
         <v>8</v>
@@ -3817,7 +3817,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" ht="14">
       <c r="A35" s="30" t="s">
         <v>64</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="13.5" thickBot="1">
+    <row r="36" spans="1:4" ht="14" thickBot="1">
       <c r="A36" s="31"/>
       <c r="B36" s="35">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" ht="14">
       <c r="A37" s="26" t="s">
         <v>65</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="13.5" thickBot="1">
+    <row r="38" spans="1:4" ht="14" thickBot="1">
       <c r="A38" s="27"/>
       <c r="B38" s="33">
         <v>14</v>
@@ -3863,7 +3863,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" ht="14">
       <c r="A39" s="30" t="s">
         <v>66</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="13.5" thickBot="1">
+    <row r="40" spans="1:4" ht="14" thickBot="1">
       <c r="A40" s="31"/>
       <c r="B40" s="35">
         <v>24</v>
@@ -3886,7 +3886,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" ht="14">
       <c r="A41" s="26" t="s">
         <v>67</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="13.5" thickBot="1">
+    <row r="42" spans="1:4" ht="14" thickBot="1">
       <c r="A42" s="27"/>
       <c r="B42" s="33">
         <v>21</v>
@@ -3909,7 +3909,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" ht="14">
       <c r="A43" s="30" t="s">
         <v>68</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="13.5" thickBot="1">
+    <row r="44" spans="1:4" ht="14" thickBot="1">
       <c r="A44" s="31"/>
       <c r="B44" s="35">
         <v>25</v>
@@ -3932,7 +3932,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" ht="14">
       <c r="A45" s="26" t="s">
         <v>69</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>3929</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="13.5" thickBot="1">
+    <row r="46" spans="1:4" ht="14" thickBot="1">
       <c r="A46" s="27"/>
       <c r="B46" s="33">
         <v>45</v>
@@ -3955,7 +3955,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" ht="14">
       <c r="A47" s="30" t="s">
         <v>70</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>5765</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="13.5" thickBot="1">
+    <row r="48" spans="1:4" ht="14" thickBot="1">
       <c r="A48" s="31"/>
       <c r="B48" s="35">
         <v>64</v>
@@ -3978,7 +3978,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" ht="14">
       <c r="A49" s="26" t="s">
         <v>71</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="13.5" thickBot="1">
+    <row r="50" spans="1:4" ht="14" thickBot="1">
       <c r="A50" s="27"/>
       <c r="B50" s="33">
         <v>14</v>
@@ -4001,7 +4001,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" ht="14">
       <c r="A51" s="30" t="s">
         <v>72</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="13.5" thickBot="1">
+    <row r="52" spans="1:4" ht="14" thickBot="1">
       <c r="A52" s="31"/>
       <c r="B52" s="35">
         <v>75</v>
@@ -4024,7 +4024,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" ht="14">
       <c r="A53" s="26" t="s">
         <v>73</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="13.5" thickBot="1">
+    <row r="54" spans="1:4" ht="14" thickBot="1">
       <c r="A54" s="27"/>
       <c r="B54" s="33">
         <v>139</v>
@@ -4047,7 +4047,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" ht="14">
       <c r="A55" s="30" t="s">
         <v>74</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="13.5" thickBot="1">
+    <row r="56" spans="1:4" ht="14" thickBot="1">
       <c r="A56" s="31"/>
       <c r="B56" s="35">
         <v>14</v>
@@ -4070,7 +4070,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" ht="14">
       <c r="A57" s="26" t="s">
         <v>75</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="13.5" thickBot="1">
+    <row r="58" spans="1:4" ht="14" thickBot="1">
       <c r="A58" s="27"/>
       <c r="B58" s="33">
         <v>3</v>
@@ -4093,7 +4093,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" ht="14">
       <c r="A59" s="30" t="s">
         <v>76</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="13.5" thickBot="1">
+    <row r="60" spans="1:4" ht="14" thickBot="1">
       <c r="A60" s="31"/>
       <c r="B60" s="35">
         <v>0</v>
@@ -4116,7 +4116,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" ht="14">
       <c r="A61" s="26" t="s">
         <v>77</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="13.5" thickBot="1">
+    <row r="62" spans="1:4" ht="14" thickBot="1">
       <c r="A62" s="27"/>
       <c r="B62" s="33">
         <v>15</v>
@@ -4139,7 +4139,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" ht="14">
       <c r="A63" s="30" t="s">
         <v>78</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="13.5" thickBot="1">
+    <row r="64" spans="1:4" ht="14" thickBot="1">
       <c r="A64" s="31"/>
       <c r="B64" s="35">
         <v>6</v>
@@ -4162,7 +4162,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" ht="14">
       <c r="A65" s="26" t="s">
         <v>79</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>2694</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="13.5" thickBot="1">
+    <row r="66" spans="1:4" ht="14" thickBot="1">
       <c r="A66" s="27"/>
       <c r="B66" s="33">
         <v>16</v>
@@ -4185,7 +4185,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" ht="14">
       <c r="A67" s="30" t="s">
         <v>80</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="13.5" thickBot="1">
+    <row r="68" spans="1:4" ht="14" thickBot="1">
       <c r="A68" s="31"/>
       <c r="B68" s="35">
         <v>10</v>
@@ -4208,7 +4208,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" ht="14">
       <c r="A69" s="26" t="s">
         <v>81</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>9539</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="13.5" thickBot="1">
+    <row r="70" spans="1:4" ht="14" thickBot="1">
       <c r="A70" s="27"/>
       <c r="B70" s="33">
         <v>41</v>
@@ -4231,7 +4231,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" ht="14">
       <c r="A71" s="30" t="s">
         <v>82</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="13.5" thickBot="1">
+    <row r="72" spans="1:4" ht="14" thickBot="1">
       <c r="A72" s="31"/>
       <c r="B72" s="35">
         <v>37</v>
@@ -4254,7 +4254,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" ht="14">
       <c r="A73" s="26" t="s">
         <v>83</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="13.5" thickBot="1">
+    <row r="74" spans="1:4" ht="14" thickBot="1">
       <c r="A74" s="27"/>
       <c r="B74" s="33">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" ht="14">
       <c r="A75" s="30" t="s">
         <v>84</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>2801</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="13.5" thickBot="1">
+    <row r="76" spans="1:4" ht="14" thickBot="1">
       <c r="A76" s="31"/>
       <c r="B76" s="35">
         <v>40</v>
@@ -4300,7 +4300,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" ht="14">
       <c r="A77" s="26" t="s">
         <v>85</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="13.5" thickBot="1">
+    <row r="78" spans="1:4" ht="14" thickBot="1">
       <c r="A78" s="27"/>
       <c r="B78" s="33">
         <v>8</v>
@@ -4323,7 +4323,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" ht="14">
       <c r="A79" s="30" t="s">
         <v>86</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="13.5" thickBot="1">
+    <row r="80" spans="1:4" ht="14" thickBot="1">
       <c r="A80" s="31"/>
       <c r="B80" s="35">
         <v>75</v>
@@ -4346,7 +4346,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" ht="14">
       <c r="A81" s="26" t="s">
         <v>87</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>3247</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="13.5" thickBot="1">
+    <row r="82" spans="1:4" ht="14" thickBot="1">
       <c r="A82" s="27"/>
       <c r="B82" s="33">
         <v>51</v>
@@ -4369,7 +4369,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" ht="14">
       <c r="A83" s="30" t="s">
         <v>88</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="13.5" thickBot="1">
+    <row r="84" spans="1:4" ht="14" thickBot="1">
       <c r="A84" s="31"/>
       <c r="B84" s="35">
         <v>82</v>
@@ -4392,7 +4392,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" ht="14">
       <c r="A85" s="26" t="s">
         <v>89</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="13.5" thickBot="1">
+    <row r="86" spans="1:4" ht="14" thickBot="1">
       <c r="A86" s="27"/>
       <c r="B86" s="33">
         <v>18</v>
@@ -4415,7 +4415,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" ht="14">
       <c r="A87" s="30" t="s">
         <v>90</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="13.5" thickBot="1">
+    <row r="88" spans="1:4" ht="14" thickBot="1">
       <c r="A88" s="31"/>
       <c r="B88" s="35">
         <v>2</v>
@@ -4438,7 +4438,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" ht="14">
       <c r="A89" s="26" t="s">
         <v>91</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="13.5" thickBot="1">
+    <row r="90" spans="1:4" ht="14" thickBot="1">
       <c r="A90" s="27"/>
       <c r="B90" s="33">
         <v>33</v>
@@ -4461,7 +4461,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" ht="14">
       <c r="A91" s="30" t="s">
         <v>92</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="13.5" thickBot="1">
+    <row r="92" spans="1:4" ht="14" thickBot="1">
       <c r="A92" s="31"/>
       <c r="B92" s="35">
         <v>96</v>
@@ -4484,7 +4484,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" ht="14">
       <c r="A93" s="26" t="s">
         <v>93</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="13.5" thickBot="1">
+    <row r="94" spans="1:4" ht="14" thickBot="1">
       <c r="A94" s="27"/>
       <c r="B94" s="33">
         <v>17</v>
@@ -4507,7 +4507,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" ht="14">
       <c r="A95" s="30" t="s">
         <v>94</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="13.5" thickBot="1">
+    <row r="96" spans="1:4" ht="14" thickBot="1">
       <c r="A96" s="31"/>
       <c r="B96" s="35">
         <v>35</v>
@@ -4530,7 +4530,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" ht="14">
       <c r="A97" s="26" t="s">
         <v>95</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>3651</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="13.5" thickBot="1">
+    <row r="98" spans="1:4" ht="14" thickBot="1">
       <c r="A98" s="27"/>
       <c r="B98" s="33">
         <v>237</v>
@@ -4553,7 +4553,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" ht="14">
       <c r="A99" s="30" t="s">
         <v>96</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="13.5" thickBot="1">
+    <row r="100" spans="1:4" ht="14" thickBot="1">
       <c r="A100" s="31"/>
       <c r="B100" s="35">
         <v>209</v>
@@ -4576,7 +4576,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" ht="14">
       <c r="A101" s="26" t="s">
         <v>97</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="13.5" thickBot="1">
+    <row r="102" spans="1:4" ht="14" thickBot="1">
       <c r="A102" s="27"/>
       <c r="B102" s="33">
         <v>19</v>
@@ -4599,7 +4599,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" ht="14">
       <c r="A103" s="30" t="s">
         <v>98</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="13.5" thickBot="1">
+    <row r="104" spans="1:4" ht="14" thickBot="1">
       <c r="A104" s="31"/>
       <c r="B104" s="35">
         <v>6</v>
@@ -4622,7 +4622,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" ht="14">
       <c r="A105" s="30" t="s">
         <v>99</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="13.5" thickBot="1">
+    <row r="106" spans="1:4" ht="14" thickBot="1">
       <c r="A106" s="31"/>
       <c r="B106" s="33">
         <v>6</v>
@@ -4645,7 +4645,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" ht="14">
       <c r="A107" s="28" t="s">
         <v>100</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>143771</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="13.5" thickBot="1">
+    <row r="108" spans="1:4" ht="14" thickBot="1">
       <c r="A108" s="29"/>
       <c r="B108" s="46">
         <v>2994</v>
@@ -4680,13 +4680,13 @@
       </c>
       <c r="B112" s="24"/>
     </row>
-    <row r="113" spans="1:2" ht="26.1" customHeight="1">
+    <row r="113" spans="1:2" ht="26" customHeight="1">
       <c r="A113" s="24" t="s">
         <v>103</v>
       </c>
       <c r="B113" s="24"/>
     </row>
-    <row r="114" spans="1:2" ht="38.1" customHeight="1">
+    <row r="114" spans="1:2" ht="38" customHeight="1">
       <c r="A114" s="25" t="s">
         <v>104</v>
       </c>
@@ -4700,10 +4700,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEAA39A-62A5-445D-B760-FE77953FA5EE}">
   <dimension ref="A1:AF9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -5051,7 +5051,7 @@
     <row r="4" spans="1:32">
       <c r="AE4" s="47"/>
     </row>
-    <row r="5" spans="1:32" ht="15.75" thickBot="1">
+    <row r="5" spans="1:32" ht="16" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>157</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="15.75" thickBot="1">
+    <row r="6" spans="1:32" ht="16" thickBot="1">
       <c r="A6" s="53" t="str">
         <f>About!B1</f>
         <v>Delaware</v>
@@ -5298,10 +5298,10 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
